--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_24.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_24.xlsx
@@ -471,74 +471,74 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91758</v>
+        <v>41262</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Olivia Nascimento</t>
+          <t>Lucca Jesus</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45081</v>
+        <v>45094</v>
       </c>
       <c r="G2" t="n">
-        <v>9788.5</v>
+        <v>7739.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89797</v>
+        <v>58564</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ana Luiza Moura</t>
+          <t>Davi Moura</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45094</v>
+        <v>45103</v>
       </c>
       <c r="G3" t="n">
-        <v>9739.379999999999</v>
+        <v>11833.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>22214</v>
+        <v>14175</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eloah Viana</t>
+          <t>Dra. Ana Clara Moura</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -547,216 +547,216 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45089</v>
+        <v>45106</v>
       </c>
       <c r="G4" t="n">
-        <v>9023.959999999999</v>
+        <v>3275.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9712</v>
+        <v>27740</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Joana Silveira</t>
+          <t>Sofia da Rocha</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45089</v>
+        <v>45084</v>
       </c>
       <c r="G5" t="n">
-        <v>6599.87</v>
+        <v>8863.620000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>52144</v>
+        <v>77612</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marina Jesus</t>
+          <t>Srta. Camila Barros</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45089</v>
+        <v>45100</v>
       </c>
       <c r="G6" t="n">
-        <v>6427.09</v>
+        <v>3141.42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61007</v>
+        <v>34003</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ana Beatriz Souza</t>
+          <t>Gabrielly da Rocha</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45094</v>
+        <v>45082</v>
       </c>
       <c r="G7" t="n">
-        <v>2875.26</v>
+        <v>8738.120000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>37333</v>
+        <v>35241</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fernando Cavalcanti</t>
+          <t>Srta. Juliana Lopes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45091</v>
+        <v>45086</v>
       </c>
       <c r="G8" t="n">
-        <v>3560.97</v>
+        <v>9868.190000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8384</v>
+        <v>63632</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Henrique Jesus</t>
+          <t>Julia Sales</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45100</v>
+        <v>45093</v>
       </c>
       <c r="G9" t="n">
-        <v>3091.94</v>
+        <v>4775.31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>15700</v>
+        <v>31714</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dr. Erick Duarte</t>
+          <t>Giovanna Azevedo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45084</v>
+        <v>45079</v>
       </c>
       <c r="G10" t="n">
-        <v>7965.55</v>
+        <v>8310.290000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>39606</v>
+        <v>23072</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ana Laura Fogaça</t>
+          <t>Dra. Ana Julia Fernandes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45099</v>
+        <v>45086</v>
       </c>
       <c r="G11" t="n">
-        <v>9305.459999999999</v>
+        <v>8444.76</v>
       </c>
     </row>
   </sheetData>
